--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>53:30</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>68:33</t>
+          <t>28:32</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>40:16</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>26:05</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>59:34</t>
+          <t>29:32</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>34:11</t>
+          <t>24:09</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,22 +2823,22 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.4%</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>58:43</t>
+          <t>28:41</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>04:34</t>
+          <t>04:33</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,12 +3215,12 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>07:14</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>37:29</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,22 +3607,22 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -3827,10 +3827,10 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>54:04</t>
+          <t>24:02</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>40:16</t>
+          <t>30:14</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
     </row>
@@ -4684,16 +4684,16 @@
         <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>9</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>44:40</t>
+          <t>24:39</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,17 +4800,17 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>28:25</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>05:48</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
     </row>
@@ -5272,10 +5272,10 @@
         <v>19</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>48:22</t>
+          <t>28:20</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,22 +5388,22 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
         <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>39:24</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>47:52</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -5860,10 +5860,10 @@
         <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,12 +5976,12 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>32:12</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -6448,16 +6448,16 @@
         <v>11</v>
       </c>
       <c r="T46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>29:57</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.7%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>94</v>
       </c>
       <c r="T48" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>29</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>11</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1534,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2315,10 +2315,10 @@
         <v>11</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>106</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>3</v>
@@ -4488,7 +4488,7 @@
         <v>15</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X37" t="n">
         <v>9</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -5272,10 +5272,10 @@
         <v>19</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -5468,7 +5468,7 @@
         <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>8</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6448,16 +6448,16 @@
         <v>11</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>94</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X48" t="n">
         <v>29</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_389_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>8</v>
@@ -692,20 +692,20 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>11</v>
       </c>
       <c r="N3" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>93.55</t>
+          <t>90.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1576,25 +1576,25 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -3111,10 +3111,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3503,14 +3503,14 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y28" t="n">
         <v>3</v>
       </c>
-      <c r="Y28" t="n">
-        <v>4</v>
-      </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA28" t="n">
@@ -3839,14 +3839,14 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,10 +3872,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
@@ -3883,14 +3883,14 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -4696,10 +4696,10 @@
         <v>3</v>
       </c>
       <c r="X37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -6796,14 +6796,14 @@
         <v>6</v>
       </c>
       <c r="X48" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="Y48" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
